--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.06658182445418</v>
+        <v>5.698319546473805</v>
       </c>
       <c r="D2" t="n">
-        <v>36.28723251127239</v>
+        <v>5.896675283081764</v>
       </c>
       <c r="E2" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F2" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.76145650483804</v>
+        <v>2.561236682036182</v>
       </c>
       <c r="D3" t="n">
-        <v>15.31331091552048</v>
+        <v>2.488413023772078</v>
       </c>
       <c r="E3" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F3" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.17356537331965</v>
+        <v>5.228204373164444</v>
       </c>
       <c r="D4" t="n">
-        <v>31.14186944446216</v>
+        <v>5.060553784725101</v>
       </c>
       <c r="E4" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F4" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47139552076654</v>
+        <v>8.039101772124562</v>
       </c>
       <c r="D5" t="n">
-        <v>48.35311930109167</v>
+        <v>7.857381886427397</v>
       </c>
       <c r="E5" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F5" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.32524713701073</v>
+        <v>5.902852659764243</v>
       </c>
       <c r="D6" t="n">
-        <v>35.65250335352173</v>
+        <v>5.793531794947281</v>
       </c>
       <c r="E6" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F6" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.15319150353589</v>
+        <v>6.037393619324583</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9509394979561</v>
+        <v>6.004527668417866</v>
       </c>
       <c r="E7" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F7" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.96551818800246</v>
+        <v>5.6818967055504</v>
       </c>
       <c r="D8" t="n">
-        <v>34.59731998135767</v>
+        <v>5.622064496970622</v>
       </c>
       <c r="E8" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F8" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.13635055617051</v>
+        <v>7.334656965377707</v>
       </c>
       <c r="D9" t="n">
-        <v>44.94597779794281</v>
+        <v>7.303721392165706</v>
       </c>
       <c r="E9" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F9" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.38945595704584</v>
+        <v>7.375786593019949</v>
       </c>
       <c r="D10" t="n">
-        <v>45.23255787993054</v>
+        <v>7.350290655488712</v>
       </c>
       <c r="E10" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F10" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.0260952342293</v>
+        <v>8.45424047556226</v>
       </c>
       <c r="D11" t="n">
-        <v>51.70733643139025</v>
+        <v>8.402442170100917</v>
       </c>
       <c r="E11" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F11" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.98613331468933</v>
+        <v>3.572746663637016</v>
       </c>
       <c r="D12" t="n">
-        <v>21.65539274694875</v>
+        <v>3.519001321379172</v>
       </c>
       <c r="E12" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F12" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>58.00525623138557</v>
+        <v>9.425854137600156</v>
       </c>
       <c r="D13" t="n">
-        <v>57.78921599051669</v>
+        <v>9.390747598458963</v>
       </c>
       <c r="E13" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F13" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.44163171335511</v>
+        <v>4.621765153420205</v>
       </c>
       <c r="D14" t="n">
-        <v>28.49253999835865</v>
+        <v>4.630037749733281</v>
       </c>
       <c r="E14" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F14" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>47.12809129264556</v>
+        <v>7.658314835054904</v>
       </c>
       <c r="D15" t="n">
-        <v>46.93225966147105</v>
+        <v>7.626492194989046</v>
       </c>
       <c r="E15" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F15" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.48056313535993</v>
+        <v>7.553091509495989</v>
       </c>
       <c r="D16" t="n">
-        <v>46.63453158592524</v>
+        <v>7.578111382712851</v>
       </c>
       <c r="E16" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F16" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.82518022659613</v>
+        <v>8.096591786821872</v>
       </c>
       <c r="D17" t="n">
-        <v>50.05508014955165</v>
+        <v>8.133950524302143</v>
       </c>
       <c r="E17" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F17" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>11.14476739226203</v>
+        <v>1.811024701242581</v>
       </c>
       <c r="D18" t="n">
-        <v>11.52731369771848</v>
+        <v>1.873188475879253</v>
       </c>
       <c r="E18" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F18" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>14.83712857530347</v>
+        <v>2.411033393486814</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99811344361553</v>
+        <v>2.437193434587523</v>
       </c>
       <c r="E19" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F19" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>21.89896736777569</v>
+        <v>3.55858219726355</v>
       </c>
       <c r="D20" t="n">
-        <v>22.05166259729646</v>
+        <v>3.583395172060674</v>
       </c>
       <c r="E20" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F20" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>27.74478957445342</v>
+        <v>4.508528305848681</v>
       </c>
       <c r="D21" t="n">
-        <v>28.05288194629036</v>
+        <v>4.558593316272184</v>
       </c>
       <c r="E21" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F21" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>35.68881345054775</v>
+        <v>5.799432185714009</v>
       </c>
       <c r="D22" t="n">
-        <v>36.04707712087186</v>
+        <v>5.857650032141677</v>
       </c>
       <c r="E22" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F22" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>67.56721023248062</v>
+        <v>10.9796716627781</v>
       </c>
       <c r="D23" t="n">
-        <v>67.9347864118012</v>
+        <v>11.03940279191769</v>
       </c>
       <c r="E23" t="n">
-        <v>14.31292048112556</v>
+        <v>2.325849578182903</v>
       </c>
       <c r="F23" t="n">
-        <v>14.27802916440047</v>
+        <v>2.320179739215076</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
